--- a/data/trans_orig/Hacinamiento-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Hacinamiento-Provincia-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número de personas que viven en el hogar</t>
+          <t>Número de personas que viven en el hogar (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +638,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -726,12 +726,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 1,5</t>
+          <t>1,31; 1,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,39</t>
+          <t>1,21; 1,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -741,44 +741,44 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,27; 1,75</t>
+          <t>1,29; 1,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 1,53</t>
+          <t>1,32; 1,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,25; 1,39</t>
+          <t>1,26; 1,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 1,21</t>
+          <t>1,11; 1,21</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 1,62</t>
+          <t>1,3; 1,6</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 1,48</t>
+          <t>1,35; 1,48</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,25; 1,36</t>
+          <t>1,25; 1,37</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -861,42 +861,42 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,34</t>
+          <t>1,2; 1,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,32; 1,47</t>
+          <t>1,31; 1,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 1,33</t>
+          <t>1,22; 1,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 1,38</t>
+          <t>1,22; 1,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>1,22; 1,35</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,31; 1,42</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1,21; 1,37</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,31; 1,42</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1,21; 1,36</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,26; 1,37</t>
+          <t>1,27; 1,37</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,27; 1,44</t>
+          <t>1,27; 1,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1006,27 +1006,27 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,12; 1,27</t>
+          <t>1,12; 1,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 1,46</t>
+          <t>1,29; 1,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 1,37</t>
+          <t>1,22; 1,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 1,37</t>
+          <t>1,22; 1,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 1,3</t>
+          <t>1,13; 1,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1041,17 +1041,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 1,35</t>
+          <t>1,24; 1,34</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 1,26</t>
+          <t>1,15; 1,25</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,27; 1,4</t>
+          <t>1,26; 1,39</t>
         </is>
       </c>
     </row>
@@ -1141,17 +1141,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,34</t>
+          <t>1,21; 1,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,37; 1,59</t>
+          <t>1,38; 1,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,4</t>
+          <t>1,2; 1,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1161,17 +1161,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 1,46</t>
+          <t>1,26; 1,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,21; 1,44</t>
+          <t>1,22; 1,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 1,32</t>
+          <t>1,15; 1,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,31; 1,47</t>
+          <t>1,32; 1,48</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,31</t>
+          <t>1,19; 1,31</t>
         </is>
       </c>
     </row>
@@ -1276,17 +1276,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,18; 1,58</t>
+          <t>1,18; 1,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,09; 1,49</t>
+          <t>1,09; 1,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,23; 1,42</t>
+          <t>1,22; 1,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1296,12 +1296,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,26; 1,78</t>
+          <t>1,26; 1,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,12; 1,51</t>
+          <t>1,13; 1,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1311,17 +1311,17 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,2</t>
+          <t>0,99; 1,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,27; 1,58</t>
+          <t>1,28; 1,59</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,15; 1,45</t>
+          <t>1,14; 1,41</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1331,14 +1331,14 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,01; 1,13</t>
+          <t>1,01; 1,14</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,83; 1,02</t>
+          <t>0,82; 1,02</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,19; 1,33</t>
+          <t>1,19; 1,32</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,33; 1,5</t>
+          <t>1,32; 1,49</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1461,24 +1461,24 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,22; 1,32</t>
+          <t>1,22; 1,33</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,86; 1,0</t>
+          <t>0,85; 1,01</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,27; 1,39</t>
+          <t>1,28; 1,39</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,22 +1556,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,22; 1,33</t>
+          <t>1,21; 1,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,34; 1,46</t>
+          <t>1,34; 1,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,07; 1,19</t>
+          <t>1,08; 1,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,26; 1,38</t>
+          <t>1,26; 1,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1581,17 +1581,17 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,34; 1,44</t>
+          <t>1,34; 1,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,1; 1,21</t>
+          <t>1,1; 1,2</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,3; 1,52</t>
+          <t>1,31; 1,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,35; 1,44</t>
+          <t>1,36; 1,44</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,31; 1,43</t>
+          <t>1,31; 1,44</t>
         </is>
       </c>
     </row>
@@ -1701,12 +1701,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,26; 1,36</t>
+          <t>1,25; 1,36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,16; 1,26</t>
+          <t>1,17; 1,27</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,25; 1,3</t>
+          <t>1,25; 1,31</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">

--- a/data/trans_orig/Hacinamiento-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Hacinamiento-Provincia-trans_orig.xlsx
@@ -716,12 +716,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 1,25</t>
+          <t>1,11; 1,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,27; 1,56</t>
+          <t>1,26; 1,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,21; 1,39</t>
+          <t>1,21; 1,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,29; 1,73</t>
+          <t>1,28; 1,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,26; 1,39</t>
+          <t>1,25; 1,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -761,17 +761,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 1,6</t>
+          <t>1,31; 1,62</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 1,48</t>
+          <t>1,34; 1,49</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,25; 1,37</t>
+          <t>1,25; 1,36</t>
         </is>
       </c>
     </row>
@@ -856,12 +856,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 1,41</t>
+          <t>1,28; 1,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,35</t>
+          <t>1,21; 1,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 1,32</t>
+          <t>1,21; 1,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 1,35</t>
+          <t>1,21; 1,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -891,12 +891,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 1,37</t>
+          <t>1,22; 1,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 1,37</t>
+          <t>1,26; 1,37</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -996,32 +996,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,27; 1,45</t>
+          <t>1,27; 1,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 1,37</t>
+          <t>1,23; 1,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,12; 1,26</t>
+          <t>1,13; 1,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 1,48</t>
+          <t>1,29; 1,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 1,38</t>
+          <t>1,21; 1,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 1,36</t>
+          <t>1,21; 1,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1046,12 +1046,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 1,25</t>
+          <t>1,15; 1,26</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 1,39</t>
+          <t>1,28; 1,4</t>
         </is>
       </c>
     </row>
@@ -1141,42 +1141,42 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,21; 1,34</t>
+          <t>1,19; 1,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 1,61</t>
+          <t>1,38; 1,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,38</t>
+          <t>1,21; 1,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,21; 1,4</t>
+          <t>1,21; 1,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,26; 1,48</t>
+          <t>1,26; 1,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,22; 1,44</t>
+          <t>1,22; 1,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 1,31</t>
+          <t>1,15; 1,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,31</t>
+          <t>1,2; 1,33</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 1,48</t>
+          <t>1,31; 1,47</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1276,42 +1276,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,18; 1,59</t>
+          <t>1,19; 1,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,09; 1,47</t>
+          <t>1,09; 1,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,22; 1,42</t>
+          <t>1,23; 1,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,99; 1,15</t>
+          <t>0,98; 1,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,26; 1,82</t>
+          <t>1,25; 1,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,13; 1,51</t>
+          <t>1,12; 1,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 1,27</t>
+          <t>1,04; 1,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,99; 1,18</t>
+          <t>0,99; 1,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,14; 1,41</t>
+          <t>1,15; 1,42</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,19; 1,32</t>
+          <t>1,18; 1,32</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,32; 1,49</t>
+          <t>1,33; 1,5</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,19; 1,28</t>
+          <t>1,18; 1,28</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,85; 1,01</t>
+          <t>0,85; 1,0</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1561,17 +1561,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,34; 1,47</t>
+          <t>1,33; 1,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,08; 1,2</t>
+          <t>1,07; 1,19</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,26; 1,39</t>
+          <t>1,26; 1,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,31; 1,52</t>
+          <t>1,31; 1,53</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,25; 1,33</t>
+          <t>1,24; 1,33</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,04; 1,13</t>
+          <t>1,05; 1,14</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,17; 1,23</t>
+          <t>1,17; 1,24</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,25; 1,3</t>
+          <t>1,24; 1,29</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,22; 1,27</t>
+          <t>1,21; 1,27</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">

--- a/data/trans_orig/Hacinamiento-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Hacinamiento-Provincia-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,54 +648,54 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,14</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,43</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1,42</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1,31</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>1,18</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1,4</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1,4</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,28</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,14</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,43</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1,26</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1,16</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>1,42</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1,31</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1,16</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1,42</t>
-        </is>
-      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
           <t>1,41</t>
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,3</t>
+          <t>1,29</t>
         </is>
       </c>
     </row>
@@ -716,47 +716,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 1,24</t>
+          <t>1,08; 1,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,26; 1,55</t>
+          <t>1,27; 1,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 1,5</t>
+          <t>1,32; 1,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,21; 1,38</t>
+          <t>1,25; 1,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 1,22</t>
+          <t>1,12; 1,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,28; 1,75</t>
+          <t>1,27; 1,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 1,52</t>
+          <t>1,32; 1,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,25; 1,4</t>
+          <t>1,2; 1,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 1,21</t>
+          <t>1,12; 1,21</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 1,49</t>
+          <t>1,34; 1,48</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,25; 1,36</t>
+          <t>1,25; 1,34</t>
         </is>
       </c>
     </row>
@@ -788,62 +788,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1,3</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,28</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,36</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1,28</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>1,33</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>1,27</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>1,39</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1,26</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1,32</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>1,27</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,3</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,28</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,36</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1,28</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1,32</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>1,37</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>1,27</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1,37</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>1,28</t>
         </is>
       </c>
     </row>
@@ -856,42 +856,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,28; 1,41</t>
+          <t>1,22; 1,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 1,35</t>
+          <t>1,21; 1,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,31; 1,47</t>
+          <t>1,31; 1,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 1,32</t>
+          <t>1,21; 1,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 1,39</t>
+          <t>1,27; 1,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 1,36</t>
+          <t>1,2; 1,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,31; 1,42</t>
+          <t>1,32; 1,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 1,36</t>
+          <t>1,21; 1,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 1,32</t>
+          <t>1,22; 1,32</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,27</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,28</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1,3</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1,34</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1,29</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>1,2</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>1,37</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,27</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,28</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,2</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1,3</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -996,42 +996,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,27; 1,43</t>
+          <t>1,21; 1,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 1,36</t>
+          <t>1,22; 1,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 1,27</t>
+          <t>1,13; 1,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 1,47</t>
+          <t>1,23; 1,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 1,37</t>
+          <t>1,27; 1,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 1,36</t>
+          <t>1,23; 1,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 1,29</t>
+          <t>1,12; 1,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 1,38</t>
+          <t>1,29; 1,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 1,34</t>
+          <t>1,24; 1,35</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 1,4</t>
+          <t>1,27; 1,39</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1,28</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,34</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,32</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1,22</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>1,21</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1,27</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1,47</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,26</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,28</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,34</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,32</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,22</t>
+          <t>1,25</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1136,47 +1136,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1,21; 1,4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1,25; 1,46</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1,21; 1,44</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1,15; 1,33</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>1,15; 1,28</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1,19; 1,33</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1,38; 1,6</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1,21; 1,38</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1,21; 1,41</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,26; 1,47</t>
+          <t>1,2; 1,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,22; 1,43</t>
+          <t>1,37; 1,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 1,3</t>
+          <t>1,19; 1,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,33</t>
+          <t>1,2; 1,31</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 1,31</t>
+          <t>1,19; 1,29</t>
         </is>
       </c>
     </row>
@@ -1208,44 +1208,44 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,41</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,28</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,14</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1,04</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>1,39</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>1,23</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>1,32</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>1,06</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,41</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,28</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,14</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>1,06</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
           <t>1,4</t>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,06</t>
+          <t>1,05</t>
         </is>
       </c>
     </row>
@@ -1276,52 +1276,52 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,19; 1,58</t>
+          <t>1,26; 1,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,09; 1,46</t>
+          <t>1,12; 1,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>1,05; 1,27</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0,98; 1,11</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,18; 1,58</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,09; 1,49</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
           <t>1,23; 1,42</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0,98; 1,16</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1,25; 1,73</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,12; 1,49</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,04; 1,25</t>
-        </is>
-      </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,99; 1,19</t>
+          <t>1,0; 1,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,28; 1,59</t>
+          <t>1,27; 1,58</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,15; 1,42</t>
+          <t>1,15; 1,45</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,01; 1,14</t>
+          <t>1,0; 1,11</t>
         </is>
       </c>
     </row>
@@ -1353,37 +1353,37 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>1,25</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0,94</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1,4</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,23</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>1,29</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>0,91</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>1,23</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1,23</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1,25</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,94</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1,4</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1,18; 1,29</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1,19; 1,33</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0,84; 1,05</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>1,34; 1,5</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>1,16; 1,32</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>1,21; 1,39</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>0,82; 1,02</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0,83; 1,02</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>1,18; 1,29</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>1,18; 1,29</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>1,18; 1,32</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>0,84; 1,05</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1,33; 1,5</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,18; 1,28</t>
+          <t>1,19; 1,28</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,22; 1,33</t>
+          <t>1,22; 1,32</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,85; 1,0</t>
+          <t>0,86; 1,0</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,28; 1,39</t>
+          <t>1,27; 1,38</t>
         </is>
       </c>
     </row>
@@ -1488,42 +1488,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1,3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1,39</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1,15</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1,4</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>1,27</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>1,4</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>1,12</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>1,32</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,3</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,39</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,15</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>1,39</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1556,52 +1556,52 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,21; 1,33</t>
+          <t>1,25; 1,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,33; 1,47</t>
+          <t>1,34; 1,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>1,1; 1,21</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1,32; 1,53</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1,22; 1,33</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1,34; 1,46</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
           <t>1,07; 1,19</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1,26; 1,38</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1,25; 1,36</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1,34; 1,45</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>1,1; 1,2</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,31; 1,53</t>
+          <t>1,27; 1,38</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,24; 1,33</t>
+          <t>1,25; 1,33</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,36; 1,44</t>
+          <t>1,35; 1,44</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,31; 1,44</t>
+          <t>1,31; 1,43</t>
         </is>
       </c>
     </row>
@@ -1628,42 +1628,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1,32</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1,23</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1,19</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1,06</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>1,27</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>1,31</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>1,21</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>1,08</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>1,32</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,23</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>1,19</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1,06</t>
+          <t>1,09</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1696,44 +1696,44 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1,26; 1,37</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1,19; 1,28</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1,15; 1,23</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1,02; 1,1</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>1,23; 1,32</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>1,25; 1,36</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1,17; 1,27</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1,26; 1,36</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1,16; 1,26</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>1,05; 1,14</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>1,26; 1,37</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>1,19; 1,28</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1,15; 1,23</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1,02; 1,1</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
           <t>1,26; 1,33</t>
@@ -1746,12 +1746,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,17; 1,24</t>
+          <t>1,17; 1,23</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,04; 1,1</t>
+          <t>1,04; 1,11</t>
         </is>
       </c>
     </row>
@@ -1768,62 +1768,62 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1,28</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1,31</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1,22</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1,25</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>1,27</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>1,32</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>1,24</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1,23</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1,27</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>1,31</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>1,23</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>1,24</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>1,28</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1,31</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,22</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>1,25</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>1,27</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>1,31</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>1,23</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>1,25</t>
         </is>
       </c>
     </row>
@@ -1836,44 +1836,44 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,24; 1,29</t>
+          <t>1,25; 1,3</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
+          <t>1,28; 1,34</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>1,19; 1,25</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>1,22; 1,28</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1,25; 1,3</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
           <t>1,29; 1,35</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>1,21; 1,27</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>1,22; 1,27</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>1,21; 1,26</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>1,25; 1,31</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>1,28; 1,34</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>1,19; 1,25</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>1,23; 1,29</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
           <t>1,26; 1,29</t>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,23; 1,27</t>
+          <t>1,22; 1,26</t>
         </is>
       </c>
     </row>
